--- a/vse-loti/340094471/spec-340094471.xlsx
+++ b/vse-loti/340094471/spec-340094471.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -35,11 +36,11 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -82,14 +83,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -519,34 +525,75 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Трубы стальные эл/сварные прямошовные</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>720×10</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>п.м.</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>44.125</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>3827423.88</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>86740.48</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>104088.58</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>44.125</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>3827423.88</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G4" s="8" t="n">
         <v>3827423.88</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Источник: Извещение.docx</t>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Источник: Приложение к ТЗ - спецификация.xls</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:B7"/>
+    <mergeCell ref="A6:B8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
